--- a/thesis_tables.xlsx
+++ b/thesis_tables.xlsx
@@ -51,9 +51,9 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="9">'Table 3.5'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="9">'Table 3.5'!$A$1:$C$11</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="10">'Table 3.6'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="10">'Table 3.6'!$A$1:$B$15</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="10">'Table 3.6'!$A$1:$B$16</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="11">'Table 3.7'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="11">'Table 3.7'!$A$1:$C$12</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="11">'Table 3.7'!$A$1:$C$13</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="12">'Table 3.8'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="12">'Table 3.8'!$A$1:$C$10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="13">'Table 3.9'!$4:$4</definedName>
@@ -61,7 +61,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="14">'Table 3.10'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="14">'Table 3.10'!$A$1:$C$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="15">'Table 3.11'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="15">'Table 3.11'!$A$1:$D$11</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="15">'Table 3.11'!$A$1:$D$10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="16">'Table 3.12'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="16">'Table 3.12'!$A$1:$C$11</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="17">'Table 3.13'!$4:$4</definedName>
@@ -73,7 +73,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="20">'Table 4.1'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="20">'Table 4.1'!$A$1:$B$11</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="21">'Table 4.2'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="21">'Table 4.2'!$A$1:$B$10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="21">'Table 4.2'!$A$1:$B$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -290,8 +290,8 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="Table_3_6" displayName="Table_3_6" ref="A4:B15" headerRowCount="1">
-  <autoFilter ref="A4:B15"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="Table_3_6" displayName="Table_3_6" ref="A4:B16" headerRowCount="1">
+  <autoFilter ref="A4:B16"/>
   <tableColumns count="2">
     <tableColumn id="1" name="Material"/>
     <tableColumn id="2" name="Quantity or Role"/>
@@ -301,8 +301,8 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="Table_3_7" displayName="Table_3_7" ref="A4:C12" headerRowCount="1">
-  <autoFilter ref="A4:C12"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="Table_3_7" displayName="Table_3_7" ref="A4:C13" headerRowCount="1">
+  <autoFilter ref="A4:C13"/>
   <tableColumns count="3">
     <tableColumn id="1" name="Item"/>
     <tableColumn id="2" name="Purpose"/>
@@ -348,8 +348,8 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="Table_3_11" displayName="Table_3_11" ref="A4:D11" headerRowCount="1">
-  <autoFilter ref="A4:D11"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="Table_3_11" displayName="Table_3_11" ref="A4:D10" headerRowCount="1">
+  <autoFilter ref="A4:D10"/>
   <tableColumns count="4">
     <tableColumn id="1" name="File or Module"/>
     <tableColumn id="2" name="Target"/>
@@ -436,8 +436,8 @@
 </file>
 
 <file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="21" name="Table_4_2" displayName="Table_4_2" ref="A4:B10" headerRowCount="1">
-  <autoFilter ref="A4:B10"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="21" name="Table_4_2" displayName="Table_4_2" ref="A4:B11" headerRowCount="1">
+  <autoFilter ref="A4:B11"/>
   <tableColumns count="2">
     <tableColumn id="1" name="Evaluation Area"/>
     <tableColumn id="2" name="Required Measurement"/>
@@ -1242,7 +1242,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29.35" customWidth="1" min="1" max="1"/>
-    <col width="19.15" customWidth="1" min="2" max="2"/>
+    <col width="23.4" customWidth="1" min="2" max="2"/>
     <col width="18.3" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>"Find the chair."</t>
+          <t>"Find the green marker."</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>"Find the chair."</t>
+          <t>"Find the green marker."</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>"Find the chair."</t>
+          <t>"Find the green marker."</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>"Find the chair."</t>
+          <t>"Find the green marker."</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>"Find the chair."</t>
+          <t>"Find the green marker."</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>"Find the chair."</t>
+          <t>"Find the green marker."</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
@@ -1415,7 +1415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31.9" customWidth="1" min="1" max="1"/>
@@ -1451,7 +1451,7 @@
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>Coral Dev Board</t>
+          <t>Raspberry Pi 4</t>
         </is>
       </c>
       <c r="B5" s="9" t="inlineStr">
@@ -1460,7 +1460,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
+    <row r="6" ht="75" customHeight="1">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>ESP32</t>
@@ -1468,7 +1468,7 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>Sensor, safety, UART, and motor-control controller</t>
+          <t>Sensor, safety, USB serial, and motor-control controller</t>
         </is>
       </c>
     </row>
@@ -1559,22 +1559,34 @@
     <row r="14" ht="45" customHeight="1">
       <c r="A14" s="10" t="inlineStr">
         <is>
+          <t>Coloured marker</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>Repeatable first visual landmark</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="45" customHeight="1">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
           <t>Instruction and scenario list</t>
         </is>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>Common experimental inputs</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="90" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
+    <row r="16" ht="90" customHeight="1">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>JSONL result logs</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>Store prompts, detections, sensors, actions, latency, and failures</t>
         </is>
@@ -1599,12 +1611,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21.7" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
-    <col width="47.2" customWidth="1" min="3" max="3"/>
+    <col width="27.65" customWidth="1" min="1" max="1"/>
+    <col width="51.45" customWidth="1" min="2" max="2"/>
+    <col width="41.25" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -1641,7 +1653,7 @@
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>Coral operating system</t>
+          <t>Raspberry Pi operating system</t>
         </is>
       </c>
       <c r="B5" s="9" t="inlineStr">
@@ -1651,7 +1663,7 @@
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>Mendel Linux</t>
+          <t>Raspberry Pi OS Lite 64-bit</t>
         </is>
       </c>
     </row>
@@ -1663,7 +1675,7 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>Prompt parser, detection control, validation, UART, and logging</t>
+          <t>Prompt parser, grounding, validation, serial, and logging</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
@@ -1672,7 +1684,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1">
+    <row r="7" ht="45" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Webcam processing</t>
@@ -1680,7 +1692,7 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Capture RGB frames</t>
+          <t>Capture and process RGB frames</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
@@ -1706,24 +1718,24 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="75" customHeight="1">
+    <row r="9" ht="45" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>Visual grounding</t>
+          <t>Initial visual grounding</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Detect supported target class</t>
+          <t>Detect supported coloured marker</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>Quantized Edge TPU-compiled TensorFlow Lite detector</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="60" customHeight="1">
+          <t>OpenCV HSV segmentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="75" customHeight="1">
       <c r="A10" s="10" t="inlineStr">
         <is>
           <t>ESP32 firmware</t>
@@ -1731,7 +1743,7 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>Sensors, safety, UART, and two-MX1508 motor control</t>
+          <t>Sensors, safety, USB serial, and two-MX1508 motor control</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
@@ -1740,7 +1752,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="45" customHeight="1">
+    <row r="11" ht="60" customHeight="1">
       <c r="A11" s="9" t="inlineStr">
         <is>
           <t>Communication</t>
@@ -1748,12 +1760,12 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Coral to ESP32 commands and status</t>
+          <t>Raspberry Pi to ESP32 commands and status</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>UART3 to UART2 at 115200 baud</t>
+          <t>USB serial at 115200 baud</t>
         </is>
       </c>
     </row>
@@ -1771,6 +1783,23 @@
       <c r="C12" s="10" t="inlineStr">
         <is>
           <t>JSONL</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>Future grounding</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Detect indoor objects and landmarks</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>OpenCV DNN, TensorFlow Lite, or API-based VLM</t>
         </is>
       </c>
     </row>
@@ -1797,8 +1826,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16.6" customWidth="1" min="1" max="1"/>
-    <col width="35.3" customWidth="1" min="2" max="2"/>
-    <col width="25.95" customWidth="1" min="3" max="3"/>
+    <col width="30.2" customWidth="1" min="2" max="2"/>
+    <col width="31.9" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -1845,7 +1874,7 @@
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>find the chair</t>
+          <t>find the green marker</t>
         </is>
       </c>
     </row>
@@ -1862,7 +1891,7 @@
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>green marker</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1903,12 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Important detected instruction objects</t>
+          <t>Important instruction objects</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>["chair"]</t>
+          <t>["green marker"]</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1942,7 @@
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>find and approach the chair</t>
+          <t>find and approach the green marker</t>
         </is>
       </c>
     </row>
@@ -2001,7 +2030,7 @@
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>Target not detected</t>
+          <t>Marker not detected</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
@@ -2013,7 +2042,7 @@
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>Target centre is left of the image centre zone</t>
+          <t>Marker centre is left of the image centre zone</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
@@ -2025,7 +2054,7 @@
     <row r="8" ht="60" customHeight="1">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>Target centre is right of the image centre zone</t>
+          <t>Marker centre is right of the image centre zone</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
@@ -2037,7 +2066,7 @@
     <row r="9" ht="60" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>Target is centred and below the goal-size threshold</t>
+          <t>Marker is centred and below the goal-size threshold</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
@@ -2049,7 +2078,7 @@
     <row r="10" ht="60" customHeight="1">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>Target reaches the configured image-area threshold</t>
+          <t>Marker reaches the configured image-area threshold</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
@@ -2058,10 +2087,10 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
+    <row r="11" ht="45" customHeight="1">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>ESP32 reports obstacle</t>
+          <t>ESP32 reports obstacle or sensor fault</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
@@ -2232,7 +2261,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52.3" customWidth="1" min="1" max="1"/>
@@ -2280,7 +2309,7 @@
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>docs/coral_dev_board_full_software_setup.md</t>
+          <t>docs/raspberry_pi_4_full_software_setup.md</t>
         </is>
       </c>
       <c r="B5" s="9" t="inlineStr">
@@ -2290,7 +2319,7 @@
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>Complete Coral OS-to-final-result setup</t>
+          <t>Raspberry Pi OS-to-final-result setup</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
@@ -2299,7 +2328,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
+    <row r="6" ht="75" customHeight="1">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>docs/circuit_wiring_guide.md</t>
@@ -2312,7 +2341,7 @@
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>Exact Coral, ESP32, sensor, and MX1508 wiring</t>
+          <t>Exact Raspberry Pi, ESP32, sensor, and MX1508 wiring</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr">
@@ -2346,17 +2375,17 @@
     <row r="8" ht="90" customHeight="1">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>src/coral_robot/robot_controller.py</t>
+          <t>src/raspberry_pi_robot/robot_controller.py</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>Coral Dev Board</t>
+          <t>Raspberry Pi 4</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>Prompt parser, Edge TPU detection, action selection, UART, and logging</t>
+          <t>Prompt parser, OpenCV grounding, action selection, USB serial, and logging</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
@@ -2390,42 +2419,20 @@
     <row r="10" ht="75" customHeight="1">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>docker-compose.laptop-demo.yml</t>
+          <t>firmware/esp32_robot_controller/esp32_robot_controller.ino</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>Docker laptop demo</t>
+          <t>ESP32</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>Reproducible container build and runtime configuration</t>
+          <t>USB serial, sensors, safety, and four-motor control</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>Provided</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="75" customHeight="1">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>firmware/esp32_robot_controller/esp32_robot_controller.ino</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>ESP32</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>UART, sensors, safety, and four-motor control</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
         <is>
           <t>Provided</t>
         </is>
@@ -2536,14 +2543,14 @@
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>Detection and action metrics</t>
+          <t>Grounding and action metrics</t>
         </is>
       </c>
     </row>
     <row r="8" ht="75" customHeight="1">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>T_total = T_prompt + T_capture + T_detection + T_sensor + T_comm</t>
+          <t>T_total = T_prompt + T_capture + T_grounding + T_sensor + T_comm</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
@@ -2553,14 +2560,14 @@
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>Coral latency</t>
+          <t>Raspberry Pi latency</t>
         </is>
       </c>
     </row>
     <row r="9" ht="90" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>a_exec = stop for invalid output, high uncertainty, obstacle, timeout, or invalid action</t>
+          <t>a_exec = stop for invalid output, high uncertainty, obstacle, sensor fault, timeout, or invalid action</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
@@ -2631,7 +2638,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="51.45" customWidth="1" min="2" max="2"/>
+    <col width="44.65" customWidth="1" min="2" max="2"/>
     <col width="33.59999999999999" customWidth="1" min="3" max="3"/>
     <col width="46.35" customWidth="1" min="4" max="4"/>
   </cols>
@@ -2694,7 +2701,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="75" customHeight="1">
+    <row r="6" ht="60" customHeight="1">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Stage 2</t>
@@ -2702,7 +2709,7 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>Wire Coral UART3, ESP32, sensors, and both MX1508 drivers</t>
+          <t>Wire ESP32, sensors, and both MX1508 drivers</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
@@ -2716,7 +2723,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="45" customHeight="1">
+    <row r="7" ht="60" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Stage 3</t>
@@ -2724,12 +2731,12 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Flash ESP32 firmware</t>
+          <t>Flash ESP32 and connect it to Raspberry Pi by USB</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>UART PING and sensor status test</t>
+          <t>PING and sensor-status test</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
@@ -2768,17 +2775,17 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Install Mendel Linux and test Edge TPU and webcam</t>
+          <t>Install Raspberry Pi OS and test webcam</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>Official demos and camera capture</t>
+          <t>Camera capture test</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>Working Coral platform</t>
+          <t>Working Raspberry Pi platform</t>
         </is>
       </c>
     </row>
@@ -2790,7 +2797,7 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>Run Coral controller without --execute</t>
+          <t>Run Raspberry Pi controller without --execute</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
@@ -2800,7 +2807,7 @@
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>Correct prompt, detection, action, and STOP command</t>
+          <t>Correct prompt, grounding, action, and STOP command</t>
         </is>
       </c>
     </row>
@@ -2871,7 +2878,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.3" customWidth="1" min="1" max="1"/>
-    <col width="48.05" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
     <col width="29.35" customWidth="1" min="3" max="3"/>
     <col width="34.45" customWidth="1" min="4" max="4"/>
   </cols>
@@ -2934,7 +2941,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1">
+    <row r="6" ht="45" customHeight="1">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Webcam test</t>
@@ -2942,7 +2949,7 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>USB webcam on Coral</t>
+          <t>USB webcam on Raspberry Pi</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
@@ -2959,17 +2966,17 @@
     <row r="7" ht="45" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>Edge TPU test</t>
+          <t>Grounding test</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Supported target in controlled views</t>
+          <t>Supported marker in controlled views</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>Detection correctness</t>
+          <t>Grounding correctness</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
@@ -2981,12 +2988,12 @@
     <row r="8" ht="45" customHeight="1">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>UART test</t>
+          <t>USB serial test</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>Coral UART3 and ESP32 UART2</t>
+          <t>Raspberry Pi and ESP32</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
@@ -3066,7 +3073,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
+    <row r="12" ht="90" customHeight="1">
       <c r="A12" s="10" t="inlineStr">
         <is>
           <t>Safety test</t>
@@ -3074,7 +3081,7 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>Obstacle, timeout, invalid command, and uncertainty</t>
+          <t>Obstacle, sensor fault, timeout, invalid command, and uncertainty</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
@@ -3096,7 +3103,7 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Controlled chair target</t>
+          <t>Controlled green marker</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
@@ -3371,7 +3378,7 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Percentage of correctly detected target conditions</t>
+          <t>Percentage of correctly grounded marker conditions</t>
         </is>
       </c>
     </row>
@@ -3402,7 +3409,7 @@
     <row r="10" ht="75" customHeight="1">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>UART reliability</t>
+          <t>USB serial reliability</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
@@ -3514,7 +3521,7 @@
     <row r="5" ht="75" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>Clear supported instruction</t>
+          <t>Clear supported marker instruction</t>
         </is>
       </c>
       <c r="B5" s="9" t="inlineStr">
@@ -3538,7 +3545,7 @@
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>Target not visible</t>
+          <t>Marker not visible</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
@@ -3550,7 +3557,7 @@
     <row r="8" ht="45" customHeight="1">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>Target visible on left or right</t>
+          <t>Marker visible on left or right</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
@@ -3562,7 +3569,7 @@
     <row r="9" ht="45" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>Target centred and not close</t>
+          <t>Marker centred and not close</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
@@ -3574,7 +3581,7 @@
     <row r="10" ht="45" customHeight="1">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>Target reaches configured goal size</t>
+          <t>Marker reaches configured goal size</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
@@ -3614,10 +3621,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18.3" customWidth="1" min="1" max="1"/>
+    <col width="23.4" customWidth="1" min="1" max="1"/>
     <col width="55" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -3667,53 +3674,65 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>Target detection correctness and safe missing-target behaviour</t>
+          <t>Marker-grounding correctness and safe missing-target behaviour</t>
         </is>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>Coral performance</t>
+          <t>Raspberry Pi performance</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Edge TPU inference and end-to-end action latency</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="90" customHeight="1">
+          <t>OpenCV processing and end-to-end action latency</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="45" customHeight="1">
       <c r="A8" s="10" t="inlineStr">
         <is>
+          <t>USB communication</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Command and sensor-status reliability</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="90" customHeight="1">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
           <t>Sensors and safety</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>Ultrasonic error, GY-291 response, timeout, and safe-stop success</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>Robot movement</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>Action correctness and simple-goal completion rate</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="75" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
+    <row r="11" ht="75" customHeight="1">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>Power system</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>Voltage stability, resets, current, and operating duration</t>
         </is>
@@ -4172,17 +4191,17 @@
     <row r="6" ht="90" customHeight="1">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>Coral Dev Board</t>
+          <t>Raspberry Pi 4</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>Related to low-power embedded Edge TPU deployment rather than the original LM-Nav platform</t>
+          <t>Related to low-cost onboard Linux robot-compute platforms</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>Suitable when the visual model can be converted to an Edge TPU-compatible TFLite model</t>
+          <t>Suitable for Python, OpenCV, USB devices, lightweight inference, and flexible development</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr">
@@ -4526,7 +4545,7 @@
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>Build one focused low-cost Coral Dev Board prototype with ESP32 sensor, safety, and motor control</t>
+          <t>Build one focused low-cost Raspberry Pi 4 prototype with ESP32 sensor, safety, and motor control</t>
         </is>
       </c>
     </row>
@@ -4687,12 +4706,12 @@
     <row r="6" ht="90" customHeight="1">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>Objective 2: Integrate one Coral Dev Board physical robot</t>
+          <t>Objective 2: Integrate one Raspberry Pi 4 physical robot</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>Connect Coral, ESP32, webcam, sensors, MX1508 drivers, motors, and completed power system</t>
+          <t>Connect Raspberry Pi, ESP32, webcam, sensors, MX1508 drivers, motors, and completed power system</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
@@ -4702,7 +4721,7 @@
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>Wiring, sensor, motor, UART, and power tests</t>
+          <t>Wiring, sensor, motor, USB serial, and power tests</t>
         </is>
       </c>
     </row>
@@ -4724,7 +4743,7 @@
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>Detection correctness, action accuracy, safe-stop rate, and goal completion</t>
+          <t>Grounding correctness, action accuracy, safe-stop rate, and goal completion</t>
         </is>
       </c>
     </row>
@@ -4820,7 +4839,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="75" customHeight="1">
+    <row r="7" ht="90" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Stage 3</t>
@@ -4828,7 +4847,7 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Wire ESP32 sensors, Coral UART3, and two MX1508 drivers</t>
+          <t>Wire ESP32 sensors and two MX1508 drivers, then connect Raspberry Pi USB devices</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
@@ -4862,12 +4881,12 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Install Mendel Linux and verify USB webcam and Edge TPU detector</t>
+          <t>Install Raspberry Pi OS and verify webcam and USB serial</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>Working Coral perception platform</t>
+          <t>Working Raspberry Pi platform</t>
         </is>
       </c>
     </row>
@@ -4879,7 +4898,7 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>Integrate structured prompt processing, detection, action selection, UART, and logging</t>
+          <t>Integrate structured prompt processing, OpenCV grounding, action selection, and logging</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
@@ -4960,12 +4979,12 @@
     <row r="5" ht="90" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>Coral Dev Board</t>
+          <t>Raspberry Pi 4</t>
         </is>
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>Onboard prompt processing, webcam capture, Edge TPU-compatible detection, action selection, and logging</t>
+          <t>Onboard prompt processing, webcam capture, OpenCV grounding, action selection, and logging</t>
         </is>
       </c>
     </row>
@@ -4977,7 +4996,7 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>UART communication, sensor reading, deterministic safety, and motor control</t>
+          <t>USB serial communication, sensor reading, deterministic safety, and motor control</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5082,7 @@
   <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24.25" customWidth="1" min="1" max="1"/>
+    <col width="30.2" customWidth="1" min="1" max="1"/>
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="23.4" customWidth="1" min="3" max="3"/>
     <col width="43.8" customWidth="1" min="4" max="4"/>
@@ -5113,7 +5132,7 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>Accept a basic supported goal such as find the chair</t>
+          <t>Accept a supported goal such as find the green marker</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
@@ -5152,12 +5171,12 @@
     <row r="7" ht="90" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>Coral onboard processing</t>
+          <t>Raspberry Pi onboard processing</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Run prompt parser, webcam, detection, action selection, and logging onboard</t>
+          <t>Run prompt parser, webcam, grounding, action selection, and logging onboard</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
@@ -5167,19 +5186,19 @@
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>Coral completes the navigation loop</t>
+          <t>Raspberry Pi completes the navigation loop</t>
         </is>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>Edge TPU visual grounding</t>
+          <t>Webcam visual grounding</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>Detect a supported target class</t>
+          <t>Detect a supported coloured marker</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
@@ -5189,14 +5208,14 @@
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>Correct detection or safe search response</t>
+          <t>Correct grounding or safe search response</t>
         </is>
       </c>
     </row>
     <row r="9" ht="60" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>Coral-to-ESP32 UART</t>
+          <t>Raspberry Pi-to-ESP32 USB serial</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
@@ -5206,7 +5225,7 @@
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>UART test</t>
+          <t>Serial test</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
@@ -5237,7 +5256,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="75" customHeight="1">
+    <row r="11" ht="90" customHeight="1">
       <c r="A11" s="9" t="inlineStr">
         <is>
           <t>Local safety</t>
@@ -5245,7 +5264,7 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Obstacle, timeout, or invalid command stops movement</t>
+          <t>Obstacle, sensor fault, timeout, or invalid command stops movement</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
